--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,91 +413,119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121.19707</v>
+        <v>16.85159</v>
       </c>
       <c r="D2" t="n">
-        <v>86.68177</v>
+        <v>16.70923</v>
       </c>
       <c r="E2" t="n">
-        <v>90.6354</v>
+        <v>16.80352</v>
       </c>
       <c r="F2" t="n">
-        <v>516.2533</v>
+        <v>42.86542</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.7962</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>121.51929</v>
+        <v>16.59216</v>
       </c>
       <c r="D3" t="n">
-        <v>84.58316000000001</v>
+        <v>16.31056</v>
       </c>
       <c r="E3" t="n">
-        <v>89.50933999999999</v>
+        <v>16.38265</v>
       </c>
       <c r="F3" t="n">
-        <v>517.87514</v>
+        <v>42.33341</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05009</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.80953</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>121.55456</v>
+        <v>16.56921</v>
       </c>
       <c r="D4" t="n">
-        <v>87.1729</v>
+        <v>16.38706</v>
       </c>
       <c r="E4" t="n">
-        <v>89.24193</v>
+        <v>16.49031</v>
       </c>
       <c r="F4" t="n">
-        <v>511.29542</v>
+        <v>41.29353</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.81757</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>123.59451</v>
+        <v>16.8502</v>
       </c>
       <c r="D5" t="n">
-        <v>87.55045</v>
+        <v>16.39623</v>
       </c>
       <c r="E5" t="n">
-        <v>89.72253000000001</v>
+        <v>16.69277</v>
       </c>
       <c r="F5" t="n">
-        <v>518.85552</v>
+        <v>42.11411</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.76512</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>118.72352</v>
+        <v>16.95149</v>
       </c>
       <c r="D6" t="n">
-        <v>84.94642</v>
+        <v>16.4365</v>
       </c>
       <c r="E6" t="n">
-        <v>90.83659</v>
+        <v>16.67547</v>
       </c>
       <c r="F6" t="n">
-        <v>521.07052</v>
+        <v>41.86098</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05024</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.81775</v>
       </c>
     </row>
     <row r="7">
@@ -545,469 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>121.58942</v>
+        <v>16.55982</v>
       </c>
       <c r="D7" t="n">
-        <v>84.78825000000001</v>
+        <v>16.37022</v>
       </c>
       <c r="E7" t="n">
-        <v>89.46111000000001</v>
+        <v>16.48628</v>
       </c>
       <c r="F7" t="n">
-        <v>516.66742</v>
+        <v>42.19679</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.80447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>119.15448</v>
+        <v>16.91369</v>
       </c>
       <c r="D8" t="n">
-        <v>84.96081</v>
+        <v>16.62039</v>
       </c>
       <c r="E8" t="n">
-        <v>90.92075</v>
+        <v>16.74747</v>
       </c>
       <c r="F8" t="n">
-        <v>513.8493999999999</v>
+        <v>42.99205</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.77388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>116.35791</v>
+        <v>16.85052</v>
       </c>
       <c r="D9" t="n">
-        <v>85.71972</v>
+        <v>16.03631</v>
       </c>
       <c r="E9" t="n">
-        <v>91.0951</v>
+        <v>16.49037</v>
       </c>
       <c r="F9" t="n">
-        <v>508.81966</v>
+        <v>42.80369</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.80471</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>120.25111</v>
+        <v>16.73537</v>
       </c>
       <c r="D10" t="n">
-        <v>86.38867999999999</v>
+        <v>16.4923</v>
       </c>
       <c r="E10" t="n">
-        <v>91.88912999999999</v>
+        <v>16.67153</v>
       </c>
       <c r="F10" t="n">
-        <v>521.00059</v>
+        <v>41.75501</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.81988</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.76966</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.47073</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.71714</v>
+      </c>
+      <c r="F11" t="n">
+        <v>41.94616</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.04999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.80487</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Micro Bump 3</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.483549999999999</v>
+        <v>16.91681</v>
       </c>
       <c r="D12" t="n">
-        <v>24.11092</v>
+        <v>16.29352</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.42782</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41.77238</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.83625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.84989</v>
+        <v>16.85983</v>
       </c>
       <c r="D13" t="n">
-        <v>23.84032</v>
+        <v>16.43737</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.52893</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.04446</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.81366</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.633179999999999</v>
+        <v>16.92351</v>
       </c>
       <c r="D14" t="n">
-        <v>24.3438</v>
+        <v>16.46684</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.50536</v>
+      </c>
+      <c r="F14" t="n">
+        <v>41.77694</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.04922</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.79852</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.545070000000001</v>
+        <v>16.87472</v>
       </c>
       <c r="D15" t="n">
-        <v>23.78514</v>
+        <v>16.34946</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.61116</v>
+      </c>
+      <c r="F15" t="n">
+        <v>41.5249</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05057</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.77002</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.52887</v>
+        <v>16.8145</v>
       </c>
       <c r="D16" t="n">
-        <v>24.03182</v>
+        <v>16.39779</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.59817</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41.90517</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.81166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.55165</v>
+        <v>16.68534</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61389</v>
+        <v>16.33503</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.53427</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41.69846</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.78733</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.559559999999999</v>
+        <v>16.62822</v>
       </c>
       <c r="D18" t="n">
-        <v>24.41546</v>
+        <v>16.48746</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.54303</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.75145</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05078</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.78849</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.3681</v>
+        <v>17.00133</v>
       </c>
       <c r="D19" t="n">
-        <v>23.95098</v>
+        <v>16.51672</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.5209</v>
+      </c>
+      <c r="F19" t="n">
+        <v>41.8654</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.04946</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.78197</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.583679999999999</v>
+        <v>16.92514</v>
       </c>
       <c r="D20" t="n">
-        <v>23.90117</v>
+        <v>16.36549</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.85873</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.16784</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.04999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.79105</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16.84843</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.35316</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.65629</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.72424</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.04967</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.78742</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.68973</v>
+        <v>16.55852</v>
       </c>
       <c r="D22" t="n">
-        <v>16.32104</v>
+        <v>16.46956</v>
       </c>
       <c r="E22" t="n">
-        <v>17.03877</v>
+        <v>16.47956</v>
       </c>
       <c r="F22" t="n">
-        <v>42.0209</v>
+        <v>41.7678</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0505</v>
+        <v>0.05033</v>
       </c>
       <c r="H22" t="n">
-        <v>1.78711</v>
+        <v>1.82141</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.6592</v>
+        <v>16.75101</v>
       </c>
       <c r="D23" t="n">
-        <v>16.34716</v>
+        <v>16.35803</v>
       </c>
       <c r="E23" t="n">
-        <v>16.50485</v>
+        <v>16.36922</v>
       </c>
       <c r="F23" t="n">
-        <v>43.38826</v>
+        <v>42.57002</v>
       </c>
       <c r="G23" t="n">
-        <v>0.05063</v>
+        <v>0.05132</v>
       </c>
       <c r="H23" t="n">
-        <v>1.80865</v>
+        <v>1.80086</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 23</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.80781</v>
+        <v>16.90533</v>
       </c>
       <c r="D24" t="n">
-        <v>16.34167</v>
+        <v>16.71472</v>
       </c>
       <c r="E24" t="n">
-        <v>16.60562</v>
+        <v>16.81944</v>
       </c>
       <c r="F24" t="n">
-        <v>41.87076</v>
+        <v>41.62786</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05156</v>
+        <v>0.04968</v>
       </c>
       <c r="H24" t="n">
-        <v>1.81593</v>
+        <v>1.80017</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 24</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.80128</v>
+        <v>16.64327</v>
       </c>
       <c r="D25" t="n">
-        <v>16.63217</v>
+        <v>16.45692</v>
       </c>
       <c r="E25" t="n">
-        <v>16.3137</v>
+        <v>16.4826</v>
       </c>
       <c r="F25" t="n">
-        <v>41.46079</v>
+        <v>42.44931</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05134</v>
+        <v>0.05114</v>
       </c>
       <c r="H25" t="n">
-        <v>1.79302</v>
+        <v>1.81176</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.42784</v>
+        <v>16.57069</v>
       </c>
       <c r="D26" t="n">
-        <v>16.61715</v>
+        <v>16.42848</v>
       </c>
       <c r="E26" t="n">
-        <v>16.43883</v>
+        <v>16.56563</v>
       </c>
       <c r="F26" t="n">
-        <v>42.62351</v>
+        <v>41.96781</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05078</v>
+        <v>0.05095</v>
       </c>
       <c r="H26" t="n">
-        <v>1.77572</v>
+        <v>1.82974</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 26</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.62232</v>
+        <v>16.76444</v>
       </c>
       <c r="D27" t="n">
-        <v>16.36919</v>
+        <v>16.58049</v>
       </c>
       <c r="E27" t="n">
-        <v>16.19841</v>
+        <v>16.58235</v>
       </c>
       <c r="F27" t="n">
-        <v>42.91198</v>
+        <v>42.17889</v>
       </c>
       <c r="G27" t="n">
-        <v>0.05074</v>
+        <v>0.05057</v>
       </c>
       <c r="H27" t="n">
-        <v>1.85146</v>
+        <v>1.77504</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.74237</v>
+        <v>16.67423</v>
       </c>
       <c r="D28" t="n">
-        <v>16.62254</v>
+        <v>16.19846</v>
       </c>
       <c r="E28" t="n">
-        <v>16.42784</v>
+        <v>16.53651</v>
       </c>
       <c r="F28" t="n">
-        <v>42.47919</v>
+        <v>42.26926</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05011</v>
+        <v>0.04978</v>
       </c>
       <c r="H28" t="n">
-        <v>1.80515</v>
+        <v>1.8157</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 28</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.61704</v>
+        <v>16.93799</v>
       </c>
       <c r="D29" t="n">
-        <v>16.40137</v>
+        <v>16.28604</v>
       </c>
       <c r="E29" t="n">
-        <v>16.65657</v>
+        <v>16.70115</v>
       </c>
       <c r="F29" t="n">
-        <v>42.5907</v>
+        <v>42.7601</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04929</v>
+        <v>0.04946</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7807</v>
+        <v>1.79617</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.8952</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.45411</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.68598</v>
+      </c>
+      <c r="F30" t="n">
+        <v>42.33394</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05053</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.80617</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>16.97537</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.12355</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.62597</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42.02193</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.04956</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.78102</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.33805</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.43527</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.44059</v>
+      </c>
+      <c r="F32" t="n">
+        <v>41.93085</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.05044</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.82288</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.84452</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.5024</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.79862</v>
+      </c>
+      <c r="F33" t="n">
+        <v>41.84551</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05112</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.81909</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.68166</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.54415</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.59054</v>
+      </c>
+      <c r="F34" t="n">
+        <v>42.33047</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.81353</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.82055</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.31035</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.75917</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.27416</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.82523</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.6096</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.33924</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.58918</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42.22318</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05017</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.77393</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.73724</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.36273</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.47248</v>
+      </c>
+      <c r="F37" t="n">
+        <v>41.68076</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.05066</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.81097</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.37435</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.08997</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.31991</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.4046</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.35007</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.68385</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.97913</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.57515</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.06579</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.90294</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>16.50732</v>
-      </c>
-      <c r="D30" t="n">
-        <v>16.44921</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16.60539</v>
-      </c>
-      <c r="F30" t="n">
-        <v>43.43517</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.0509</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.81116</v>
+      <c r="C41" t="n">
+        <v>17.08635</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15.88149</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.1874</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21.53304</v>
+      </c>
+      <c r="G41" t="n">
+        <v>33.39789</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.42883</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.78776</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15.9593</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.7167</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.22208</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.9985</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.06897</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.17975</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.98627</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.1863</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.5093</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.29679</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.4242</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.25771</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.20597</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.92513</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.13784</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.69887</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.80787</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.90176</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.87234</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.10593</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.11736</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.59739</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33.53782</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.64652</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.69316</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.3804</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.61049</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.41548</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.88868</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.66755</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.39589</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.75892</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.16301</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.76313</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.11534</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.33809</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.37791</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.77522</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.83413</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.99015</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.145</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.41998</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.48789</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16.70888</v>
+      </c>
+      <c r="D51" t="n">
+        <v>15.80346</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.23302</v>
+      </c>
+      <c r="F51" t="n">
+        <v>21.51525</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34.33482</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.24363</v>
+      </c>
+      <c r="D52" t="n">
+        <v>15.86805</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.10786</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.54248</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34.95856</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.36443</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15.8154</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.13191</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.54443</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34.38579</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16.70348</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.11272</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.32639</v>
+      </c>
+      <c r="F54" t="n">
+        <v>21.61504</v>
+      </c>
+      <c r="G54" t="n">
+        <v>33.75237</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.73087</v>
+      </c>
+      <c r="D55" t="n">
+        <v>15.7266</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.37802</v>
+      </c>
+      <c r="F55" t="n">
+        <v>21.9669</v>
+      </c>
+      <c r="G55" t="n">
+        <v>33.95276</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.33073</v>
+      </c>
+      <c r="D56" t="n">
+        <v>15.93496</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.12336</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.65492</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.44561</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.2666</v>
+      </c>
+      <c r="D57" t="n">
+        <v>15.8129</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.11281</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21.1234</v>
+      </c>
+      <c r="G57" t="n">
+        <v>33.65528</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.74561</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.00237</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.22568</v>
+      </c>
+      <c r="F58" t="n">
+        <v>21.79526</v>
+      </c>
+      <c r="G58" t="n">
+        <v>33.42595</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.75753</v>
+      </c>
+      <c r="D59" t="n">
+        <v>15.90651</v>
+      </c>
+      <c r="E59" t="n">
+        <v>15.93799</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21.45311</v>
+      </c>
+      <c r="G59" t="n">
+        <v>34.38823</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.72249</v>
+      </c>
+      <c r="D60" t="n">
+        <v>15.77816</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.3469</v>
+      </c>
+      <c r="F60" t="n">
+        <v>21.44996</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.45266</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16.30655</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15.8094</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.15852</v>
+      </c>
+      <c r="F61" t="n">
+        <v>21.59948</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34.24455</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>16.54996</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15.6319</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.38389</v>
+      </c>
+      <c r="F62" t="n">
+        <v>21.65236</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.66623</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>16.43148</v>
+      </c>
+      <c r="D63" t="n">
+        <v>15.96111</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.01836</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.56496</v>
+      </c>
+      <c r="G63" t="n">
+        <v>34.84501</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>17.07906</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16.15016</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.19544</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.9776</v>
+      </c>
+      <c r="G64" t="n">
+        <v>33.85241</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>16.43172</v>
+      </c>
+      <c r="D65" t="n">
+        <v>15.67155</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.20952</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.38733</v>
+      </c>
+      <c r="G65" t="n">
+        <v>34.04646</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>16.69245</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.08045</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.29788</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21.65157</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34.75019</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>16.53829</v>
+      </c>
+      <c r="D67" t="n">
+        <v>15.69987</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.45439</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.70308</v>
+      </c>
+      <c r="G67" t="n">
+        <v>33.91982</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>16.3619</v>
+      </c>
+      <c r="D68" t="n">
+        <v>15.67922</v>
+      </c>
+      <c r="E68" t="n">
+        <v>15.90194</v>
+      </c>
+      <c r="F68" t="n">
+        <v>21.56156</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.20703</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>16.53943</v>
+      </c>
+      <c r="D69" t="n">
+        <v>15.84358</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.24667</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20.96308</v>
+      </c>
+      <c r="G69" t="n">
+        <v>33.83689</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>16.38996</v>
+      </c>
+      <c r="D70" t="n">
+        <v>15.92423</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.31118</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.65862</v>
+      </c>
+      <c r="G70" t="n">
+        <v>34.28492</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>16.65073</v>
+      </c>
+      <c r="D71" t="n">
+        <v>15.7259</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.34793</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.28496</v>
+      </c>
+      <c r="G71" t="n">
+        <v>33.41717</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.34673</v>
+      </c>
+      <c r="D72" t="n">
+        <v>15.54805</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.26164</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.61155</v>
+      </c>
+      <c r="G72" t="n">
+        <v>34.40003</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.71548</v>
+      </c>
+      <c r="D73" t="n">
+        <v>15.83609</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.43487</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.94718</v>
+      </c>
+      <c r="G73" t="n">
+        <v>33.39196</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16.41055</v>
+      </c>
+      <c r="D74" t="n">
+        <v>15.77415</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.14269</v>
+      </c>
+      <c r="F74" t="n">
+        <v>21.35567</v>
+      </c>
+      <c r="G74" t="n">
+        <v>34.0578</v>
       </c>
     </row>
   </sheetData>
